--- a/results/result_evaluation_logs/B_Task_Modularisation_Gen1.xlsx
+++ b/results/result_evaluation_logs/B_Task_Modularisation_Gen1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X51"/>
+  <dimension ref="A1:W51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,11 +542,6 @@
       <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Result String</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Langfuse Trace ID</t>
         </is>
       </c>
     </row>
@@ -628,11 +623,6 @@
 </t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0d5b165a-66d8-44c2-a680-a75dc255ac56</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -708,11 +698,6 @@
 wd:Q20992419 wd:P31 wd:Q17516 .
 wd:Q20992419 wd:P585 wd:Q120 .
 </t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>535c0635-ab84-4cd0-8e74-f33e5fed1cce</t>
         </is>
       </c>
     </row>
@@ -797,11 +782,6 @@
 </t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>d4bb1cfc-ebbc-4991-a967-9f97a33061a8</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -817,7 +797,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -826,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -835,7 +815,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -856,7 +836,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -865,15 +845,14 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>68a50316-3ab5-4f19-b9f2-e134a639da8d</t>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -957,11 +936,6 @@
 </t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>7b68ce54-4c4a-4b30-af51-5415a0c5d3a0</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1043,11 +1017,6 @@
 </t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>50545627-ed64-4394-b2ab-4dd1cd9d2c73</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1125,11 +1094,6 @@
 </t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4bfd889c-8cdb-4f1d-944c-f92b6887bb4b</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1145,7 +1109,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1154,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1163,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1184,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1193,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1259,11 +1223,6 @@
 </t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>56595eb8-2c18-4c7a-9ee5-e5639178e0d1</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1348,11 +1307,6 @@
 </t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4f8faee5-1b15-4874-9c10-362646ea6ffc</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1398,10 +1352,10 @@
         <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q11" t="n">
         <v>8</v>
@@ -1437,11 +1391,6 @@
 </t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>441f8436-7bc0-441f-83e2-869c98771fdd</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1457,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1466,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1475,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1496,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1505,7 +1454,7 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1528,11 +1477,6 @@
 </t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>f6819c92-1571-470d-94c3-cc0eb8af1151</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1608,11 +1552,6 @@
 wd:Q271108 wd:P607 wd:Q516760.
 wd:Q516760 wd:P276 wd:Q1605654.
 </t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>c5c78be8-7659-44dd-8db2-69f84a275994</t>
         </is>
       </c>
     </row>
@@ -1697,11 +1636,6 @@
 </t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>6cd4e8c0-af08-439f-a90d-5427cb5f74f3</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1717,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1726,7 +1660,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1735,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1756,7 +1690,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1765,15 +1699,14 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>e7b6c99d-21f7-4c3c-96b2-55b181c292e6</t>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -1852,11 +1785,6 @@
 wd:Q3311362 wd:P31 wd:Q3957.
 wd:Q66117 wd:P150 wd:Q3311362.
 </t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>b8c495b3-b433-4976-b8d4-a4071427a859</t>
         </is>
       </c>
     </row>
@@ -1942,11 +1870,6 @@
 </t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>d0275e2c-0412-488e-8c72-3c782860f453</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2024,11 +1947,6 @@
 wd:Q607380 wd:P527 wd:Q12345678.
 wd:Q12345678 wd:P2548 wd:Q6933370.
 </t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>a0f27e07-d36e-4be4-ab39-da4be0581ff2</t>
         </is>
       </c>
     </row>
@@ -2114,11 +2032,6 @@
 </t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>97eaaed0-14b2-4cd3-825d-601b4684e1f1</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2195,11 +2108,6 @@
 wd:Q20671544 wd:P27 wd:Q40 .
 wd:Q20671544 wd:P106 wd:Q638522 .
 </t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>09dbd97d-317e-413e-beaa-dca5eb24f72a</t>
         </is>
       </c>
     </row>
@@ -2285,11 +2193,6 @@
 </t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>568fa2db-e042-4e95-bdb9-af2464e3a490</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2366,11 +2269,6 @@
 wd:Q17052475 wd:P31 wd:Q11348.
 wd:Q11348 wd:P1344 wd:Q395.
 </t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>a7a81838-33a3-416b-a0bc-129dc51f8a61</t>
         </is>
       </c>
     </row>
@@ -2454,11 +2352,6 @@
 </t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>b3a380cc-f268-4f0a-bfbe-549581717204</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2534,11 +2427,6 @@
 wd:Q188197 wd:P2522 wd:Q1856183 .
 wd:Q188197 wd:P2522 wd:Q674962 .
 </t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>8f828902-dcb1-4dd6-910b-9acd1e6a55f4</t>
         </is>
       </c>
     </row>
@@ -2623,11 +2511,6 @@
 </t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>024bbe77-4d3a-4c7d-9665-127867ce2bda</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2643,7 +2526,7 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2652,7 +2535,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2661,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -2682,7 +2565,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2691,7 +2574,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2757,11 +2640,6 @@
 </t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>1bd6e099-f738-4bd8-af53-0642101c5a33</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2840,11 +2718,6 @@
 </t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>27cb0914-7749-4ee2-8459-8266852d8936</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2920,11 +2793,6 @@
 wd:Q22082365 wd:P131 wd:Q965.
 wd:Q965 wd:P463 wd:Q47543.
 </t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>c6ad828c-69be-4635-ad8d-8a04e44fce5d</t>
         </is>
       </c>
     </row>
@@ -3008,11 +2876,6 @@
 </t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>4e32ca14-e3d9-4767-9fca-2d7e94da5dd6</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3028,7 +2891,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -3037,7 +2900,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -3046,7 +2909,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3067,7 +2930,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -3076,7 +2939,7 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -3142,11 +3005,6 @@
 </t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>bbafe6c0-5d45-455b-8c1d-488811fe2efe</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3227,11 +3085,6 @@
 </t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>70ea20cd-6927-44cb-90fc-adf29fe8b7a3</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3277,10 +3130,10 @@
         <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
         <v>3</v>
@@ -3308,11 +3161,6 @@
 wd:Q64876878 wd:P725 wd:Q262170 .
 wd:Q262170 wd:P725 wd:Q64876878 .
 </t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>71d01c7a-1730-42d1-a856-2de929bfe633</t>
         </is>
       </c>
     </row>
@@ -3397,11 +3245,6 @@
 </t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>c4b0560e-c074-42c3-82f2-b9b45f4ea7a5</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3417,7 +3260,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -3426,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -3435,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -3456,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3465,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -3488,11 +3331,6 @@
 </t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>35fb3282-d270-46a7-94e3-f2e0e459eb05</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3569,11 +3407,6 @@
 </t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>72772f82-bf86-473b-b8b7-c6145520798f</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3589,7 +3422,7 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -3598,7 +3431,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3607,7 +3440,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -3628,7 +3461,7 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -3637,7 +3470,7 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -3660,11 +3493,6 @@
 </t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>831c8a72-1fa6-44e0-b422-235fbae7c6c4</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3742,11 +3570,6 @@
 </t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>bd8e1f43-32e1-4216-904e-dcaedf3f77a0</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3792,10 +3615,10 @@
         <v>2</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q38" t="n">
         <v>4</v>
@@ -3828,11 +3651,6 @@
 </t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>eaa2b116-697f-414c-a4ad-3c36b58ef9f9</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3911,11 +3729,6 @@
 </t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>e228273e-4f70-4fa8-ab07-de461c7e215e</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3994,11 +3807,6 @@
 </t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>c5f9301c-7ece-4786-a226-c1b3b9a1a50c</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4044,10 +3852,10 @@
         <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q41" t="n">
         <v>3</v>
@@ -4080,11 +3888,6 @@
 </t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>1c33c092-f894-4822-af96-1c6bfd38aa75</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4130,10 +3933,10 @@
         <v>4</v>
       </c>
       <c r="O42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q42" t="n">
         <v>6</v>
@@ -4170,11 +3973,6 @@
 </t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>abac6594-c89a-4951-9c85-3e61ea80ec51</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4256,11 +4054,6 @@
 </t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>2fe6274c-0de9-4507-aa82-a0c1787eda5f</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4340,11 +4133,6 @@
 wd:Q29644512 wd:P3096 wd:Q2088358.
 wd:Q29644512 wd:P159 wd:Q148.
 </t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>e6092c62-7f92-4db7-b1a8-1f7fff116796</t>
         </is>
       </c>
     </row>
@@ -4429,11 +4217,6 @@
 </t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>61b60a3a-1704-4e77-a7ed-92d4b19fdb78</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4449,7 +4232,7 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -4458,7 +4241,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -4467,7 +4250,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -4488,7 +4271,7 @@
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -4497,7 +4280,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -4520,11 +4303,6 @@
 </t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>a3e6e497-56e7-4498-90ba-c776464d6d7b</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4606,11 +4384,6 @@
 </t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>527cace5-9ae5-49d1-a1df-535063e52faf</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4690,11 +4463,6 @@
 </t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>bb6b82b8-54f5-4000-9975-92f6709cc641</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4710,7 +4478,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -4719,7 +4487,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -4728,7 +4496,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -4749,7 +4517,7 @@
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -4758,7 +4526,7 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -4824,11 +4592,6 @@
 </t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>bf20c129-8cd1-4c1a-a45a-1172903f440b</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4844,7 +4607,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -4853,7 +4616,7 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -4862,7 +4625,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -4883,7 +4646,7 @@
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -4892,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
         <v>0</v>
@@ -4958,11 +4721,6 @@
 </t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>0efa8ab8-943f-4d62-b1db-3c1051ae0d64</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5041,11 +4799,6 @@
 </t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>235cfcf9-02ff-464d-b2ea-cdd9f7dd47fb</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
